--- a/tracker/spreadsheet/job-search-tracker.xlsx
+++ b/tracker/spreadsheet/job-search-tracker.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Every column is described in skill/job-search/references/tracker-columns.md.</t>
+          <t>Every column is described in shared/tracker-columns.md.</t>
         </is>
       </c>
     </row>
